--- a/libertadores/datasets_liberta/resultados_fase_4.xlsx
+++ b/libertadores/datasets_liberta/resultados_fase_4.xlsx
@@ -7,8 +7,8 @@
     <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
-    <sheet name="Rodada 34" sheetId="1" r:id="rId1"/>
-    <sheet name="Rodada 35" sheetId="2" r:id="rId2"/>
+    <sheet name="Rodada 15" sheetId="1" r:id="rId1"/>
+    <sheet name="Rodada 16" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -436,7 +436,7 @@
         <v>6</v>
       </c>
       <c r="B2">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="C2" t="s">
         <v>8</v>
@@ -456,7 +456,7 @@
         <v>7</v>
       </c>
       <c r="B3">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="C3" t="s">
         <v>9</v>
@@ -506,7 +506,7 @@
         <v>6</v>
       </c>
       <c r="B2">
-        <v>35</v>
+        <v>16</v>
       </c>
       <c r="C2" t="s">
         <v>10</v>
@@ -526,7 +526,7 @@
         <v>7</v>
       </c>
       <c r="B3">
-        <v>35</v>
+        <v>16</v>
       </c>
       <c r="C3" t="s">
         <v>11</v>

--- a/libertadores/datasets_liberta/resultados_fase_4.xlsx
+++ b/libertadores/datasets_liberta/resultados_fase_4.xlsx
@@ -442,13 +442,13 @@
         <v>8</v>
       </c>
       <c r="D2">
-        <v>0</v>
+        <v>61.17</v>
       </c>
       <c r="E2" t="s">
         <v>10</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>48.27</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -462,13 +462,13 @@
         <v>9</v>
       </c>
       <c r="D3">
-        <v>0</v>
+        <v>39.22</v>
       </c>
       <c r="E3" t="s">
         <v>11</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>58.27</v>
       </c>
     </row>
   </sheetData>
@@ -511,14 +511,8 @@
       <c r="C2" t="s">
         <v>10</v>
       </c>
-      <c r="D2">
-        <v>0</v>
-      </c>
       <c r="E2" t="s">
         <v>8</v>
-      </c>
-      <c r="F2">
-        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -531,14 +525,8 @@
       <c r="C3" t="s">
         <v>11</v>
       </c>
-      <c r="D3">
-        <v>0</v>
-      </c>
       <c r="E3" t="s">
         <v>9</v>
-      </c>
-      <c r="F3">
-        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/libertadores/datasets_liberta/resultados_fase_4.xlsx
+++ b/libertadores/datasets_liberta/resultados_fase_4.xlsx
@@ -442,13 +442,13 @@
         <v>8</v>
       </c>
       <c r="D2">
-        <v>61.17</v>
+        <v>61.169921875</v>
       </c>
       <c r="E2" t="s">
         <v>10</v>
       </c>
       <c r="F2">
-        <v>48.27</v>
+        <v>48.27001953125</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -462,13 +462,13 @@
         <v>9</v>
       </c>
       <c r="D3">
-        <v>39.22</v>
+        <v>39.219970703125</v>
       </c>
       <c r="E3" t="s">
         <v>11</v>
       </c>
       <c r="F3">
-        <v>58.27</v>
+        <v>58.27001953125</v>
       </c>
     </row>
   </sheetData>

--- a/libertadores/datasets_liberta/resultados_fase_4.xlsx
+++ b/libertadores/datasets_liberta/resultados_fase_4.xlsx
@@ -511,8 +511,14 @@
       <c r="C2" t="s">
         <v>10</v>
       </c>
+      <c r="D2">
+        <v>87.88</v>
+      </c>
       <c r="E2" t="s">
         <v>8</v>
+      </c>
+      <c r="F2">
+        <v>81.28</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -525,8 +531,14 @@
       <c r="C3" t="s">
         <v>11</v>
       </c>
+      <c r="D3">
+        <v>83.5</v>
+      </c>
       <c r="E3" t="s">
         <v>9</v>
+      </c>
+      <c r="F3">
+        <v>114.29</v>
       </c>
     </row>
   </sheetData>

--- a/libertadores/datasets_liberta/resultados_fase_4.xlsx
+++ b/libertadores/datasets_liberta/resultados_fase_4.xlsx
@@ -512,13 +512,13 @@
         <v>10</v>
       </c>
       <c r="D2">
-        <v>87.88</v>
+        <v>87.8798828125</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
       </c>
       <c r="F2">
-        <v>81.28</v>
+        <v>81.27978515625</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -538,7 +538,7 @@
         <v>9</v>
       </c>
       <c r="F3">
-        <v>114.29</v>
+        <v>114.2900390625</v>
       </c>
     </row>
   </sheetData>
